--- a/04-output/Buyout Log & Subcontract Release Priority.xlsx
+++ b/04-output/Buyout Log & Subcontract Release Priority.xlsx
@@ -5474,7 +5474,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>DRAFTED — with PM</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
